--- a/db/tablas_procesadas/Clase_compartida.xlsx
+++ b/db/tablas_procesadas/Clase_compartida.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\Posgrado\Proyecto Titulacion\db\tablas_procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A068BA11-5E44-4196-8883-1694761E6999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F0731B4-D53A-4104-8319-D1346EE929CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="4005" windowWidth="28785" windowHeight="15345" xr2:uid="{FFF5D47F-D24D-4A58-BAAA-F7A4CE49BDA3}"/>
+    <workbookView xWindow="1500" yWindow="1500" windowWidth="17280" windowHeight="8880" xr2:uid="{FFF5D47F-D24D-4A58-BAAA-F7A4CE49BDA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -173,9 +173,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -213,7 +213,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -319,7 +319,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -461,7 +461,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -470,12 +470,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{250BB6F0-A4A2-4738-BE13-F84D149FEE6B}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -483,7 +483,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -491,7 +491,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -499,7 +499,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -507,7 +507,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -515,7 +515,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -523,7 +523,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -539,7 +539,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -547,7 +547,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -555,7 +555,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -563,7 +563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -571,7 +571,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -579,7 +579,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -587,7 +587,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -595,7 +595,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -603,7 +603,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -611,7 +611,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -619,7 +619,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -627,7 +627,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -635,7 +635,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -643,7 +643,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -651,7 +651,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -659,7 +659,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>19</v>
       </c>
